--- a/data/trans_orig/P33_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P33_R-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>77530</t>
+          <t>76180</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>113800</t>
+          <t>111696</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>110230</t>
+          <t>111017</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>152362</t>
+          <t>151659</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>198513</t>
+          <t>197848</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>254575</t>
+          <t>250979</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,31%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>571241</t>
+          <t>573345</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>607511</t>
+          <t>608861</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>533258</t>
+          <t>533961</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>575390</t>
+          <t>574603</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1116085</t>
+          <t>1119681</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1172147</t>
+          <t>1172812</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,57%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>170561</t>
+          <t>169767</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>222607</t>
+          <t>223635</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>204673</t>
+          <t>205982</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>260332</t>
+          <t>261089</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>393324</t>
+          <t>396106</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>472114</t>
+          <t>468049</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,48%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>726930</t>
+          <t>725902</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>778976</t>
+          <t>779770</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>701946</t>
+          <t>701189</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>757605</t>
+          <t>756296</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1439701</t>
+          <t>1443766</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1518491</t>
+          <t>1515709</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>79,28%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>114338</t>
+          <t>113672</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>157719</t>
+          <t>155619</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>181267</t>
+          <t>183126</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>229179</t>
+          <t>230955</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>307628</t>
+          <t>309720</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>369694</t>
+          <t>372315</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,62%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>512903</t>
+          <t>515003</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>556284</t>
+          <t>556950</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>448351</t>
+          <t>446575</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>496263</t>
+          <t>494404</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>65,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>978458</t>
+          <t>975837</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1040524</t>
+          <t>1038432</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>77,03%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>150642</t>
+          <t>150860</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>198713</t>
+          <t>196988</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>212920</t>
+          <t>214112</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>267723</t>
+          <t>269537</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>377252</t>
+          <t>378179</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>447362</t>
+          <t>450177</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>23,01%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>725693</t>
+          <t>727418</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>773764</t>
+          <t>773546</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>763987</t>
+          <t>762173</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>818790</t>
+          <t>817598</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1508754</t>
+          <t>1505939</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1578864</t>
+          <t>1577937</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,67%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>555227</t>
+          <t>554047</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>646675</t>
+          <t>649763</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>760929</t>
+          <t>761366</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>858862</t>
+          <t>861081</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1342973</t>
+          <t>1338686</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1474587</t>
+          <t>1468943</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,3%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2582930</t>
+          <t>2579842</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2674378</t>
+          <t>2675558</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2498276</t>
+          <t>2496057</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2596209</t>
+          <t>2595772</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5112156</t>
+          <t>5117800</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5243770</t>
+          <t>5248057</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>79,68%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>172918</t>
+          <t>172289</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>220939</t>
+          <t>218334</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>205157</t>
+          <t>203908</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>254631</t>
+          <t>254986</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>391981</t>
+          <t>392238</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>463847</t>
+          <t>461111</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>32,98%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>481461</t>
+          <t>484066</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>529482</t>
+          <t>530111</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,55%</t>
+          <t>68,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>441247</t>
+          <t>440892</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>490721</t>
+          <t>491970</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>63,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>934431</t>
+          <t>937167</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1006297</t>
+          <t>1006040</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>71,95%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>240359</t>
+          <t>237212</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>296296</t>
+          <t>296710</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>318606</t>
+          <t>320042</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>381398</t>
+          <t>383978</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>577947</t>
+          <t>578571</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>666788</t>
+          <t>667951</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,63%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>719667</t>
+          <t>719253</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>775604</t>
+          <t>778751</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>76,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>649722</t>
+          <t>647142</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>712514</t>
+          <t>711078</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>62,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>68,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1380295</t>
+          <t>1379132</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1469136</t>
+          <t>1468512</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>67,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>71,74%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>147236</t>
+          <t>145102</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>197854</t>
+          <t>196062</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>202365</t>
+          <t>202985</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>253926</t>
+          <t>255291</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>363165</t>
+          <t>362379</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>433979</t>
+          <t>434718</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,38%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>557764</t>
+          <t>559556</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>608382</t>
+          <t>610516</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>522266</t>
+          <t>520901</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>573827</t>
+          <t>573207</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>67,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1097831</t>
+          <t>1097092</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1168645</t>
+          <t>1169431</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>71,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>76,34%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>226124</t>
+          <t>224322</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>281956</t>
+          <t>281020</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>312356</t>
+          <t>315778</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>373019</t>
+          <t>373001</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>553316</t>
+          <t>555278</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>636972</t>
+          <t>636413</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,06%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>657622</t>
+          <t>658558</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>713454</t>
+          <t>715256</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>672749</t>
+          <t>672767</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>733412</t>
+          <t>729990</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>69,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1348374</t>
+          <t>1348933</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1432030</t>
+          <t>1430068</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>72,03%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>832387</t>
+          <t>826532</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>941945</t>
+          <t>934936</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1099157</t>
+          <t>1094611</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1219663</t>
+          <t>1216383</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1952772</t>
+          <t>1968252</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2111054</t>
+          <t>2120077</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,45%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2471615</t>
+          <t>2478624</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2581173</t>
+          <t>2587028</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>75,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2329295</t>
+          <t>2332575</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2449801</t>
+          <t>2454347</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4851463</t>
+          <t>4842440</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5009745</t>
+          <t>4994265</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>71,73%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>120603</t>
+          <t>121978</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>164215</t>
+          <t>165093</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>182591</t>
+          <t>182326</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>231246</t>
+          <t>228212</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>318175</t>
+          <t>316744</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>382987</t>
+          <t>380636</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,5%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>507067</t>
+          <t>506189</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>550679</t>
+          <t>549304</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>81,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>433208</t>
+          <t>436242</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>481863</t>
+          <t>482128</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>952749</t>
+          <t>955100</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1017561</t>
+          <t>1018992</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>71,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>76,29%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>173881</t>
+          <t>173010</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>226537</t>
+          <t>224919</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>254175</t>
+          <t>253668</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>314815</t>
+          <t>313828</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>444484</t>
+          <t>444748</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>522942</t>
+          <t>526044</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,54%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>792646</t>
+          <t>794264</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>845302</t>
+          <t>846173</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>77,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>725997</t>
+          <t>726984</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>786637</t>
+          <t>787144</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>69,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1537052</t>
+          <t>1533950</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1615510</t>
+          <t>1615246</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,41%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>174002</t>
+          <t>174651</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>225021</t>
+          <t>225132</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>213748</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>266159</t>
+          <t>271080</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>402902</t>
+          <t>403882</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>475055</t>
+          <t>478279</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,98%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>534531</t>
+          <t>534420</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>585550</t>
+          <t>584901</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>70,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>517904</t>
+          <t>512983</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>569613</t>
+          <t>570315</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1068561</t>
+          <t>1065337</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1140714</t>
+          <t>1139734</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>69,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>73,84%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>220619</t>
+          <t>221143</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>274593</t>
+          <t>277646</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>249209</t>
+          <t>247842</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>309068</t>
+          <t>308038</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>486262</t>
+          <t>481437</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>563994</t>
+          <t>563992</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>662974</t>
+          <t>659921</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>716948</t>
+          <t>716424</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>76,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>731606</t>
+          <t>732636</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>791465</t>
+          <t>792832</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>70,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>76,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1414247</t>
+          <t>1414249</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1491979</t>
+          <t>1496804</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>75,66%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>728777</t>
+          <t>735103</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>834909</t>
+          <t>838273</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>951601</t>
+          <t>952532</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1062651</t>
+          <t>1062267</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1718801</t>
+          <t>1716459</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1871601</t>
+          <t>1870789</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,04%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2552675</t>
+          <t>2549311</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2658807</t>
+          <t>2652481</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2467351</t>
+          <t>2467735</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2578401</t>
+          <t>2577470</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>69,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5045986</t>
+          <t>5046798</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5198786</t>
+          <t>5201128</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>72,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>75,19%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>135226</t>
+          <t>151528</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>115855</t>
+          <t>130651</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>157792</t>
+          <t>176553</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>217579</t>
+          <t>232408</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>198856</t>
+          <t>213895</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>236125</t>
+          <t>251978</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>352805</t>
+          <t>383935</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>322523</t>
+          <t>354656</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>380336</t>
+          <t>415856</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,93%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>486818</t>
+          <t>524808</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>464252</t>
+          <t>499783</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>506189</t>
+          <t>545685</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>439024</t>
+          <t>480474</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>420478</t>
+          <t>460904</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>457747</t>
+          <t>498987</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>70,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>925842</t>
+          <t>1005283</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>898311</t>
+          <t>973362</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>956124</t>
+          <t>1034562</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>74,47%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>622044</t>
+          <t>676336</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>622044</t>
+          <t>676336</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>622044</t>
+          <t>676336</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>656603</t>
+          <t>712882</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>656603</t>
+          <t>712882</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>656603</t>
+          <t>712882</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1278647</t>
+          <t>1389218</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1278647</t>
+          <t>1389218</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1278647</t>
+          <t>1389218</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>197133</t>
+          <t>209772</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>88047</t>
+          <t>181946</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>258223</t>
+          <t>236641</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>245787</t>
+          <t>270647</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>222191</t>
+          <t>249319</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>267203</t>
+          <t>296592</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>442920</t>
+          <t>480419</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>292241</t>
+          <t>443570</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>515047</t>
+          <t>515133</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>25,11%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>965770</t>
+          <t>811792</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>904680</t>
+          <t>784923</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1074856</t>
+          <t>839618</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>673534</t>
+          <t>758917</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>652118</t>
+          <t>732972</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>697130</t>
+          <t>780245</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1639304</t>
+          <t>1570709</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1567177</t>
+          <t>1535995</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1789983</t>
+          <t>1607558</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>78,37%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1162903</t>
+          <t>1021564</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1162903</t>
+          <t>1021564</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1162903</t>
+          <t>1021564</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>919321</t>
+          <t>1029564</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>919321</t>
+          <t>1029564</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>919321</t>
+          <t>1029564</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2082224</t>
+          <t>2051128</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2082224</t>
+          <t>2051128</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2082224</t>
+          <t>2051128</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>179637</t>
+          <t>202219</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>155612</t>
+          <t>175594</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>204241</t>
+          <t>229294</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>406440</t>
+          <t>232792</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>251135</t>
+          <t>209626</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>620018</t>
+          <t>254471</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>586077</t>
+          <t>435010</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>424421</t>
+          <t>395416</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>941937</t>
+          <t>470111</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>31,14%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>466464</t>
+          <t>539227</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>441860</t>
+          <t>512152</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>490489</t>
+          <t>565852</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>72,73%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>486920</t>
+          <t>535189</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>273342</t>
+          <t>513510</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>642225</t>
+          <t>558355</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>69,69%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>953384</t>
+          <t>1074417</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>597524</t>
+          <t>1039316</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1115040</t>
+          <t>1114011</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>71,18%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>68,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>73,8%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646101</t>
+          <t>741446</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646101</t>
+          <t>741446</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646101</t>
+          <t>741446</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>893360</t>
+          <t>767981</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>893360</t>
+          <t>767981</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>893360</t>
+          <t>767981</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1539461</t>
+          <t>1509427</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1539461</t>
+          <t>1509427</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1539461</t>
+          <t>1509427</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>262706</t>
+          <t>276728</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>233052</t>
+          <t>248748</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>291840</t>
+          <t>307721</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>341188</t>
+          <t>377228</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>277161</t>
+          <t>351405</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>375194</t>
+          <t>407634</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>603895</t>
+          <t>653956</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>528940</t>
+          <t>613875</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>647222</t>
+          <t>693924</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>33,01%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>663126</t>
+          <t>712410</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>633992</t>
+          <t>681417</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>692780</t>
+          <t>740390</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>747977</t>
+          <t>735948</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>713971</t>
+          <t>705542</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>812004</t>
+          <t>761771</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>63,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>68,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1411102</t>
+          <t>1448358</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1367775</t>
+          <t>1408390</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1486057</t>
+          <t>1488439</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>66,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>70,8%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>925832</t>
+          <t>989138</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>925832</t>
+          <t>989138</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>925832</t>
+          <t>989138</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1089165</t>
+          <t>1113176</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1089165</t>
+          <t>1113176</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1089165</t>
+          <t>1113176</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2014997</t>
+          <t>2102314</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2014997</t>
+          <t>2102314</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2014997</t>
+          <t>2102314</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>774702</t>
+          <t>840246</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>592845</t>
+          <t>787282</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>863876</t>
+          <t>894029</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1210995</t>
+          <t>1113074</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1047790</t>
+          <t>1066597</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1664509</t>
+          <t>1169690</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1985697</t>
+          <t>1953320</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1757557</t>
+          <t>1879397</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2464388</t>
+          <t>2023902</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>28,7%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2582177</t>
+          <t>2588239</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2493003</t>
+          <t>2534456</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2764034</t>
+          <t>2641203</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2347455</t>
+          <t>2510528</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1893941</t>
+          <t>2453912</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2510660</t>
+          <t>2557005</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>4929632</t>
+          <t>5098767</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4450941</t>
+          <t>5028185</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5157772</t>
+          <t>5172690</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>72,3%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>73,35%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3356879</t>
+          <t>3428485</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3356879</t>
+          <t>3428485</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3356879</t>
+          <t>3428485</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3558450</t>
+          <t>3623602</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3558450</t>
+          <t>3623602</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3558450</t>
+          <t>3623602</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>6915329</t>
+          <t>7052087</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6915329</t>
+          <t>7052087</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6915329</t>
+          <t>7052087</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
